--- a/data/trans_camb/IP11-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP11-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,27; -2,68</t>
+          <t>-15,4; -2,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 1,92</t>
+          <t>-12,74; 1,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 2,68</t>
+          <t>-12,38; 2,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 5,3</t>
+          <t>-13,57; 5,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 6,18</t>
+          <t>-13,04; 5,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 1,83</t>
+          <t>-15,91; 0,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,95; -0,44</t>
+          <t>-11,94; -0,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 2,54</t>
+          <t>-9,85; 2,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,57; -0,74</t>
+          <t>-11,8; -0,08</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 20,71</t>
+          <t>-100,0; -20,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-89,45; 85,21</t>
+          <t>-91,34; 68,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-92,25; 103,3</t>
+          <t>-90,54; 70,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-75,17; 103,35</t>
+          <t>-78,9; 96,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,05; 96,07</t>
+          <t>-73,41; 77,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-91,55; 56,03</t>
+          <t>-91,11; 38,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-82,81; -0,22</t>
+          <t>-83,91; 0,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-71,39; 41,48</t>
+          <t>-71,45; 28,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-84,69; 3,69</t>
+          <t>-83,33; 12,45</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 12,75</t>
+          <t>2,19; 12,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 7,6</t>
+          <t>-0,85; 7,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 3,86</t>
+          <t>-3,14; 3,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 13,73</t>
+          <t>3,89; 13,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 9,72</t>
+          <t>1,27; 10,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 7,03</t>
+          <t>-0,4; 7,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 11,16</t>
+          <t>4,33; 11,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,0</t>
+          <t>1,12; 7,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 4,05</t>
+          <t>-0,97; 4,02</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,9; 1510,52</t>
+          <t>25,01; 1523,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,44; 935,79</t>
+          <t>-49,69; 888,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-87,08; 486,87</t>
+          <t>-85,46; 519,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77,06; —</t>
+          <t>53,03; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,4; —</t>
+          <t>-4,67; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,58; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>122,37; 1236,87</t>
+          <t>131,9; 1329,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,0; 948,23</t>
+          <t>29,2; 847,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-39,37; 465,23</t>
+          <t>-42,53; 452,77</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 17,12</t>
+          <t>-0,86; 18,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,22; -2,01</t>
+          <t>-13,71; -1,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 1,54</t>
+          <t>-11,27; 1,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 19,92</t>
+          <t>0,72; 19,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,01; -1,31</t>
+          <t>-13,26; -1,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,54; -0,34</t>
+          <t>-12,4; 0,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 15,75</t>
+          <t>3,21; 15,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,69; -3,03</t>
+          <t>-11,95; -2,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,39; -1,34</t>
+          <t>-10,23; -1,32</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 348,2</t>
+          <t>-9,32; 414,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 18,12</t>
+          <t>-100,0; 72,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-93,18; 116,6</t>
+          <t>-100,0; 78,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,78; 406,31</t>
+          <t>0,75; 368,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 25,04</t>
+          <t>-100,0; 19,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-94,0; 14,62</t>
+          <t>-94,76; 29,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,33; 275,86</t>
+          <t>24,76; 263,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-95,14; -36,45</t>
+          <t>-95,2; -36,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-87,28; -8,67</t>
+          <t>-87,98; -5,08</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 0,19</t>
+          <t>-12,1; 0,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 4,45</t>
+          <t>-10,04; 3,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,7; -2,15</t>
+          <t>-14,04; -2,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 2,38</t>
+          <t>-12,01; 2,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 7,57</t>
+          <t>-8,21; 7,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,18; -0,48</t>
+          <t>-14,17; 0,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,87; -0,09</t>
+          <t>-10,13; -0,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 3,84</t>
+          <t>-6,67; 3,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,85; -2,61</t>
+          <t>-12,72; -3,26</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-92,49; 19,81</t>
+          <t>-91,32; 15,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-76,91; 83,09</t>
+          <t>-76,86; 85,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 7,84</t>
+          <t>-100,0; 29,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-85,53; 49,97</t>
+          <t>-85,02; 55,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-60,33; 119,44</t>
+          <t>-60,78; 123,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 31,96</t>
+          <t>-100,0; 70,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-79,97; 2,93</t>
+          <t>-80,35; 1,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-57,96; 61,56</t>
+          <t>-55,41; 48,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-96,04; -11,48</t>
+          <t>-97,16; -36,13</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 5,96</t>
+          <t>-10,12; 4,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,21; -0,29</t>
+          <t>-13,28; 0,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,34; -1,71</t>
+          <t>-14,63; -1,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 11,43</t>
+          <t>1,38; 11,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,61</t>
+          <t>0,0; 9,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,14</t>
+          <t>0,0; 7,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 5,91</t>
+          <t>-3,64; 5,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 2,61</t>
+          <t>-5,5; 2,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 1,14</t>
+          <t>-6,42; 1,25</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 281,2</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-72,95; 714,4</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-70,74; 539,16</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 224,07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,33; 21,28</t>
+          <t>4,19; 21,37</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 12,45</t>
+          <t>-2,56; 10,43</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 13,63</t>
+          <t>-0,33; 13,46</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7,38; 26,52</t>
+          <t>6,89; 28,53</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 13,41</t>
+          <t>-2,3; 14,02</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 5,58</t>
+          <t>-8,17; 5,35</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,23; 21,0</t>
+          <t>8,04; 21,35</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 10,23</t>
+          <t>-0,84; 9,74</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 7,2</t>
+          <t>-2,71; 6,44</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>32,5; —</t>
+          <t>4,92; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1878,39 +1878,39 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>54,74; 1045,66</t>
+          <t>56,69; 1174,02</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-50,31; 584,42</t>
+          <t>-41,98; 670,07</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 402,02</t>
+          <t>-100,0; 245,22</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>109,98; 997,8</t>
+          <t>109,58; 1004,46</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-25,49; 506,14</t>
+          <t>-23,82; 504,4</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-52,16; 407,19</t>
+          <t>-54,82; 356,14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 7,97</t>
+          <t>-1,44; 8,56</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,5; -0,09</t>
+          <t>-7,52; -0,23</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 2,05</t>
+          <t>-6,51; 1,58</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 11,72</t>
+          <t>-0,53; 11,9</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,81; -1,89</t>
+          <t>-10,61; -1,77</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 0,45</t>
+          <t>-8,91; 0,4</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,31; 8,51</t>
+          <t>0,36; 8,45</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,65; -2,08</t>
+          <t>-7,46; -1,77</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,65; -0,19</t>
+          <t>-6,26; -0,14</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-25,85; 235,35</t>
+          <t>-24,77; 264,58</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-91,31; 26,54</t>
+          <t>-91,35; 13,28</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-77,99; 95,22</t>
+          <t>-80,5; 59,41</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 204,86</t>
+          <t>-9,57; 192,96</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-89,49; -17,65</t>
+          <t>-88,57; -20,24</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-78,84; 19,23</t>
+          <t>-78,86; 13,9</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 155,09</t>
+          <t>4,0; 165,92</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-84,68; -34,53</t>
+          <t>-84,12; -31,52</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-70,99; -0,54</t>
+          <t>-70,2; 1,48</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 3,4</t>
+          <t>-3,26; 3,12</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 1,24</t>
+          <t>-4,16; 1,22</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,34; -0,03</t>
+          <t>-5,35; -0,17</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 0,26</t>
+          <t>-5,96; 0,56</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 2,54</t>
+          <t>-4,57; 2,82</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,8; -1,88</t>
+          <t>-7,56; -1,74</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 1,04</t>
+          <t>-3,57; 1,06</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 1,01</t>
+          <t>-3,47; 1,06</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-5,74; -1,88</t>
+          <t>-5,8; -1,72</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-63,86; 250,34</t>
+          <t>-67,19; 183,65</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-81,64; 98,53</t>
+          <t>-83,35; 98,03</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 92,55</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-82,64; 16,76</t>
+          <t>-85,3; 26,63</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-64,95; 76,32</t>
+          <t>-67,12; 86,11</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -24,45</t>
+          <t>-100,0; -3,93</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-65,24; 37,76</t>
+          <t>-68,74; 36,61</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-61,29; 37,47</t>
+          <t>-63,26; 40,29</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -43,37</t>
+          <t>-100,0; -36,31</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 4,07</t>
+          <t>0,04; 4,16</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -0,17</t>
+          <t>-3,55; -0,04</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-4,36; -1,01</t>
+          <t>-4,38; -0,85</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,69</t>
+          <t>0,93; 5,68</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,02</t>
+          <t>-2,93; 1,11</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-5,2; -1,38</t>
+          <t>-5,04; -1,29</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,21</t>
+          <t>1,17; 4,3</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-2,94; -0,09</t>
+          <t>-2,75; -0,02</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-4,16; -1,59</t>
+          <t>-4,22; -1,73</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 95,65</t>
+          <t>0,4; 96,79</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-60,67; -3,57</t>
+          <t>-57,75; 0,56</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-70,13; -21,66</t>
+          <t>-70,73; -19,59</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>13,16; 100,17</t>
+          <t>11,43; 101,8</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-39,9; 17,91</t>
+          <t>-40,04; 20,92</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-68,76; -21,63</t>
+          <t>-68,31; -24,88</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>15,59; 79,9</t>
+          <t>17,12; 83,9</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-43,63; -1,56</t>
+          <t>-41,9; 0,14</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-63,84; -31,02</t>
+          <t>-64,81; -33,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP11-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP11-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,4; -2,67</t>
+          <t>-16,26; -3,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 1,85</t>
+          <t>-13,25; 1,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 2,34</t>
+          <t>-11,9; 2,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 5,3</t>
+          <t>-13,56; 4,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 5,43</t>
+          <t>-13,12; 6,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 0,9</t>
+          <t>-16,62; 1,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,94; -0,5</t>
+          <t>-12,68; -0,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 2,13</t>
+          <t>-10,17; 2,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,8; -0,08</t>
+          <t>-12,15; -0,4</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -20,92</t>
+          <t>-100,0; 15,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-91,34; 68,01</t>
+          <t>-92,25; 63,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-90,54; 70,48</t>
+          <t>-88,96; 105,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-78,9; 96,64</t>
+          <t>-78,48; 79,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,41; 77,62</t>
+          <t>-77,06; 85,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-91,11; 38,3</t>
+          <t>-91,28; 55,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-83,91; 0,22</t>
+          <t>-84,48; 4,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-71,45; 28,3</t>
+          <t>-69,95; 33,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-83,33; 12,45</t>
+          <t>-85,96; 0,13</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>1,38</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 12,16</t>
+          <t>1,77; 12,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 7,56</t>
+          <t>-1,05; 7,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,24</t>
+          <t>-3,62; 3,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 13,43</t>
+          <t>3,88; 13,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 10,13</t>
+          <t>1,74; 9,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 7,27</t>
+          <t>-0,17; 7,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 11,25</t>
+          <t>4,34; 11,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 7,35</t>
+          <t>1,13; 7,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 4,02</t>
+          <t>-1,01; 4,13</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-3,94%</t>
+          <t>-3,32%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,38%</t>
         </is>
       </c>
     </row>
@@ -999,27 +999,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,01; 1523,29</t>
+          <t>19,99; 1423,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-49,69; 888,92</t>
+          <t>-52,6; 1030,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-85,46; 519,48</t>
+          <t>-86,96; 592,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53,03; —</t>
+          <t>60,55; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,67; —</t>
+          <t>-12,89; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>131,9; 1329,6</t>
+          <t>108,45; 1238,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,2; 847,64</t>
+          <t>17,99; 849,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,53; 452,77</t>
+          <t>-48,78; 489,62</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 18,05</t>
+          <t>-0,36; 18,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,71; -1,96</t>
+          <t>-13,84; -1,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 1,32</t>
+          <t>-11,44; 1,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 19,88</t>
+          <t>1,2; 19,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,26; -1,12</t>
+          <t>-13,27; -0,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 0,03</t>
+          <t>-12,29; -0,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 15,82</t>
+          <t>3,07; 16,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,95; -2,93</t>
+          <t>-11,34; -3,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,23; -1,32</t>
+          <t>-10,19; -0,9</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 414,03</t>
+          <t>-9,67; 390,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 72,06</t>
+          <t>-100,0; 24,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 78,0</t>
+          <t>-93,6; 99,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,75; 368,89</t>
+          <t>5,62; 380,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 19,87</t>
+          <t>-100,0; 28,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-94,76; 29,16</t>
+          <t>-93,14; 57,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,76; 263,54</t>
+          <t>29,64; 291,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-95,2; -36,2</t>
+          <t>-95,15; -40,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-87,98; -5,08</t>
+          <t>-87,65; 1,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 0,01</t>
+          <t>-12,44; -0,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 3,85</t>
+          <t>-9,78; 4,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,04; -2,54</t>
+          <t>-13,88; -2,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 2,82</t>
+          <t>-12,11; 2,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 7,26</t>
+          <t>-8,02; 7,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 0,5</t>
+          <t>-14,35; -0,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,13; -0,41</t>
+          <t>-9,98; 0,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 3,38</t>
+          <t>-6,62; 3,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,72; -3,26</t>
+          <t>-12,21; -2,69</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-91,32; 15,84</t>
+          <t>-90,87; 16,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-76,86; 85,44</t>
+          <t>-77,4; 88,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 29,53</t>
+          <t>-100,0; 14,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-85,02; 55,75</t>
+          <t>-84,38; 58,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-60,78; 123,42</t>
+          <t>-58,38; 136,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 70,75</t>
+          <t>-100,0; 32,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-80,35; 1,39</t>
+          <t>-81,14; 9,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-55,41; 48,27</t>
+          <t>-52,55; 59,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-97,16; -36,13</t>
+          <t>-96,51; -10,91</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 4,82</t>
+          <t>-11,39; 6,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 0,87</t>
+          <t>-14,98; 0,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,63; -1,69</t>
+          <t>-15,25; -1,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,38; 11,47</t>
+          <t>0,0; 11,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,83</t>
+          <t>0,0; 9,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,92</t>
+          <t>0,0; 9,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 5,98</t>
+          <t>-3,37; 5,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 2,51</t>
+          <t>-5,7; 2,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 1,25</t>
+          <t>-5,82; 1,31</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 281,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-72,95; 714,4</t>
+          <t>-69,22; 605,42</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,19; 21,37</t>
+          <t>4,26; 20,77</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 10,43</t>
+          <t>-1,57; 10,9</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 13,46</t>
+          <t>-0,78; 13,95</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6,89; 28,53</t>
+          <t>7,89; 27,86</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 14,02</t>
+          <t>-2,44; 13,29</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 5,35</t>
+          <t>-7,34; 5,2</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,04; 21,35</t>
+          <t>7,99; 21,77</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 9,74</t>
+          <t>-0,29; 10,37</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 6,44</t>
+          <t>-2,74; 7,09</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4,92; —</t>
+          <t>26,46; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-70,57; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>56,69; 1174,02</t>
+          <t>65,54; 1178,04</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-41,98; 670,07</t>
+          <t>-38,54; 625,05</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 245,22</t>
+          <t>-100,0; 357,33</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>109,58; 1004,46</t>
+          <t>96,53; 988,75</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-23,82; 504,4</t>
+          <t>-20,48; 464,71</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-54,82; 356,14</t>
+          <t>-54,51; 322,73</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 8,56</t>
+          <t>-1,32; 8,58</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,52; -0,23</t>
+          <t>-7,3; -0,06</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 1,58</t>
+          <t>-5,94; 2,15</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 11,9</t>
+          <t>-0,68; 11,27</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,61; -1,77</t>
+          <t>-11,25; -1,66</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 0,4</t>
+          <t>-9,04; 0,37</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,36; 8,45</t>
+          <t>0,79; 8,43</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,46; -1,77</t>
+          <t>-7,73; -1,95</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,26; -0,14</t>
+          <t>-6,66; -0,24</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-24,77; 264,58</t>
+          <t>-22,86; 285,63</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-91,35; 13,28</t>
+          <t>-92,44; 20,96</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-80,5; 59,41</t>
+          <t>-79,17; 86,66</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 192,96</t>
+          <t>-7,72; 199,86</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-88,57; -20,24</t>
+          <t>-89,7; -9,68</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-78,86; 13,9</t>
+          <t>-78,12; 19,84</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,0; 165,92</t>
+          <t>6,54; 166,36</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-84,12; -31,52</t>
+          <t>-84,35; -33,64</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-70,2; 1,48</t>
+          <t>-70,21; 3,33</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 3,12</t>
+          <t>-2,9; 3,27</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 1,22</t>
+          <t>-4,36; 1,23</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,35; -0,17</t>
+          <t>-5,42; -0,16</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 0,56</t>
+          <t>-6,29; 0,12</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 2,82</t>
+          <t>-4,65; 2,71</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,56; -1,74</t>
+          <t>-7,99; -1,99</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,06</t>
+          <t>-3,66; 0,93</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,06</t>
+          <t>-3,42; 1,18</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-5,8; -1,72</t>
+          <t>-5,55; -1,78</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-67,19; 183,65</t>
+          <t>-63,56; 197,4</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-83,35; 98,03</t>
+          <t>-85,11; 117,02</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 92,55</t>
+          <t>-100,0; 197,65</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-85,3; 26,63</t>
+          <t>-85,42; 27,28</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-67,12; 86,11</t>
+          <t>-65,75; 83,78</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -3,93</t>
+          <t>-100,0; -34,3</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-68,74; 36,61</t>
+          <t>-65,7; 38,1</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-63,26; 40,29</t>
+          <t>-59,44; 42,52</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -36,31</t>
+          <t>-100,0; -36,98</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-2,61</t>
+          <t>-2,6</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,16</t>
+          <t>0,04; 4,37</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,55; -0,04</t>
+          <t>-3,59; -0,04</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-4,38; -0,85</t>
+          <t>-4,37; -0,96</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,68</t>
+          <t>1,09; 5,68</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,11</t>
+          <t>-3,05; 0,91</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-5,04; -1,29</t>
+          <t>-5,14; -1,33</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,3</t>
+          <t>1,05; 4,19</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-2,75; -0,02</t>
+          <t>-2,61; -0,07</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -1,73</t>
+          <t>-4,31; -1,73</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-50,3%</t>
+          <t>-50,24%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-50,48%</t>
+          <t>-50,45%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0,4; 96,79</t>
+          <t>0,09; 101,47</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-57,75; 0,56</t>
+          <t>-57,18; 1,69</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-70,73; -19,59</t>
+          <t>-70,82; -21,23</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>11,43; 101,8</t>
+          <t>14,44; 101,7</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-40,04; 20,92</t>
+          <t>-40,33; 15,84</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-68,31; -24,88</t>
+          <t>-68,33; -23,97</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>17,12; 83,9</t>
+          <t>14,46; 78,68</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-41,9; 0,14</t>
+          <t>-41,54; -1,14</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-64,81; -33,97</t>
+          <t>-64,94; -32,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP11-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP11-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-4,52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,95</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-7,83</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-7,91</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-4,6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-4,45</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-4,52</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,95</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-7,72</t>
+          <t>-3,48</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-6,21</t>
+          <t>-5,8</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,26; -3,02</t>
+          <t>-13,58; 5,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 1,76</t>
+          <t>-12,22; 6,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 2,59</t>
+          <t>-16,07; 2,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 4,8</t>
+          <t>-16,27; -2,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 6,0</t>
+          <t>-13,18; 1,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 1,68</t>
+          <t>-11,66; 4,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,68; -0,74</t>
+          <t>-11,95; -0,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 2,41</t>
+          <t>-10,07; 2,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,15; -0,4</t>
+          <t>-12,07; -0,1</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-36,15%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-23,58%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-62,54%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-90,45%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-52,57%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-50,93%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-36,15%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-23,58%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-61,7%</t>
+          <t>-39,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-57,68%</t>
+          <t>-53,92%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 15,95</t>
+          <t>-75,17; 103,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-92,25; 63,94</t>
+          <t>-71,05; 96,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-88,96; 105,55</t>
+          <t>-91,05; 57,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-78,48; 79,19</t>
+          <t>-100,0; 20,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-77,06; 85,97</t>
+          <t>-89,45; 85,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-91,28; 55,37</t>
+          <t>-90,12; 148,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-84,48; 4,26</t>
+          <t>-82,81; -0,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,95; 33,8</t>
+          <t>-71,39; 41,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-85,96; 0,13</t>
+          <t>-83,74; 10,43</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,97</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,91</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>6,84</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,81</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,97</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,81</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>1,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 12,45</t>
+          <t>3,74; 13,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 7,75</t>
+          <t>1,24; 9,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 3,26</t>
+          <t>-0,6; 7,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 13,81</t>
+          <t>2,16; 12,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 9,82</t>
+          <t>-1,05; 7,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 7,7</t>
+          <t>-2,98; 5,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,34; 11,48</t>
+          <t>4,04; 11,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 7,04</t>
+          <t>1,36; 7,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 4,13</t>
+          <t>-0,69; 4,88</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>648,52%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>403,34%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>235,72%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>287,3%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>118,16%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-3,32%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>648,52%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>403,34%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>227,54%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>105,84%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,99; 1423,68</t>
+          <t>77,06; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-52,6; 1030,15</t>
+          <t>-16,4; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-86,96; 592,3</t>
+          <t>-72,4; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60,55; —</t>
+          <t>15,9; 1510,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,89; —</t>
+          <t>-46,44; 935,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 636,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>108,45; 1238,83</t>
+          <t>122,37; 1236,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,99; 849,81</t>
+          <t>37,0; 948,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-48,78; 489,62</t>
+          <t>-43,67; 543,74</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10,42</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-6,75</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-6,04</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>8,35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-7,12</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-5,04</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10,42</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-6,75</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,92</t>
+          <t>-5,15</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-5,5</t>
+          <t>-5,6</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 18,49</t>
+          <t>1,66; 19,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,84; -1,97</t>
+          <t>-13,01; -1,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 1,88</t>
+          <t>-12,59; -0,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 19,48</t>
+          <t>-0,55; 17,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,27; -0,98</t>
+          <t>-15,22; -2,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,29; -0,01</t>
+          <t>-12,17; 1,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,07; 16,14</t>
+          <t>2,7; 15,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,34; -3,01</t>
+          <t>-11,69; -3,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,19; -0,9</t>
+          <t>-10,46; -1,47</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>117,78%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-76,28%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-68,29%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>101,05%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-86,25%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-61,04%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>117,78%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-76,28%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-66,92%</t>
+          <t>-62,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-64,23%</t>
+          <t>-65,47%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 390,31</t>
+          <t>8,78; 406,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 24,95</t>
+          <t>-100,0; 25,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-93,6; 99,83</t>
+          <t>-94,29; 8,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,62; 380,78</t>
+          <t>-8,17; 348,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 28,57</t>
+          <t>-100,0; 18,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-93,14; 57,9</t>
+          <t>-94,68; 109,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,64; 291,66</t>
+          <t>20,33; 275,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-95,15; -40,19</t>
+          <t>-95,14; -36,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-87,65; 1,24</t>
+          <t>-87,37; -10,75</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-4,52</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,46</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-7,37</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-5,6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-2,7</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-7,78</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-4,52</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-7,49</t>
+          <t>-7,64</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-7,61</t>
+          <t>-7,51</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,44; -0,18</t>
+          <t>-11,89; 2,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 4,44</t>
+          <t>-8,27; 7,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,88; -2,23</t>
+          <t>-14,84; 0,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 2,33</t>
+          <t>-12,2; 0,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 7,5</t>
+          <t>-9,61; 4,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,35; -0,42</t>
+          <t>-13,63; -1,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 0,2</t>
+          <t>-9,87; -0,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 3,85</t>
+          <t>-7,27; 3,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,21; -2,69</t>
+          <t>-11,75; -2,19</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-44,75%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-4,53%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-72,87%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-61,39%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-29,58%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-85,23%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-44,75%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-4,53%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-74,09%</t>
+          <t>-83,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-79,05%</t>
+          <t>-78,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-90,87; 16,48</t>
+          <t>-85,53; 49,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-77,4; 88,24</t>
+          <t>-60,33; 119,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 14,34</t>
+          <t>-100,0; 43,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-84,38; 58,53</t>
+          <t>-92,49; 19,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,38; 136,02</t>
+          <t>-76,91; 83,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 32,94</t>
+          <t>-100,0; 16,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-81,14; 9,2</t>
+          <t>-79,97; 2,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-52,55; 59,42</t>
+          <t>-57,96; 61,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-96,51; -10,91</t>
+          <t>-96,43; -9,17</t>
         </is>
       </c>
     </row>
@@ -1488,34 +1488,34 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,22</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,9</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2,74</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,91</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-5,27</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>-6,67</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,22</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,9</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2,56</t>
-        </is>
-      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1,26</t>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,83</t>
+          <t>-1,78</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 6,2</t>
+          <t>1,37; 11,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 0,32</t>
+          <t>0,0; 9,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,25; -1,72</t>
+          <t>0,0; 9,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,48</t>
+          <t>-10,58; 5,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,63</t>
+          <t>-13,21; -0,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,92</t>
+          <t>-15,34; -1,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 5,27</t>
+          <t>-3,39; 5,91</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 2,77</t>
+          <t>-5,0; 2,61</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 1,31</t>
+          <t>-5,79; 1,32</t>
         </is>
       </c>
     </row>
@@ -1594,34 +1594,34 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-28,65%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-79,09%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>39,26%</t>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-56,93%</t>
+          <t>-55,24%</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-69,22; 605,42</t>
+          <t>-70,74; 539,16</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 245,41</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>16,85</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4,97</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-1,38</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>11,65</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>4,1</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>5,07</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>16,85</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>4,97</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,25</t>
+          <t>5,0</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,7</t>
+          <t>1,71</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,26; 20,77</t>
+          <t>7,38; 26,52</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 10,9</t>
+          <t>-3,24; 13,41</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 13,95</t>
+          <t>-7,24; 5,24</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7,89; 27,86</t>
+          <t>4,33; 21,28</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 13,29</t>
+          <t>-1,27; 12,45</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 5,2</t>
+          <t>-0,86; 13,4</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,99; 21,77</t>
+          <t>8,23; 21,0</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 10,37</t>
+          <t>-0,9; 10,23</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 7,09</t>
+          <t>-2,57; 7,1</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>313,23%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>92,32%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-25,74%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>480,01%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>169,19%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>209,1%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>313,23%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>92,32%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-23,23%</t>
+          <t>206,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,17%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>26,46; —</t>
+          <t>54,74; 1045,66</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>-50,31; 584,42</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 398,97</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>32,5; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>-70,57; —</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>65,54; 1178,04</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>-38,54; 625,05</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 357,33</t>
-        </is>
-      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>96,53; 988,75</t>
+          <t>109,98; 997,8</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 464,71</t>
+          <t>-25,49; 506,14</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-54,51; 322,73</t>
+          <t>-54,44; 375,68</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>5,44</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-5,89</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-3,76</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>3,3</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-3,38</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-2,11</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5,44</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-5,89</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-4,23</t>
+          <t>-2,12</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-3,15</t>
+          <t>-2,93</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 8,58</t>
+          <t>-0,2; 11,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,3; -0,06</t>
+          <t>-10,81; -1,89</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 2,15</t>
+          <t>-8,59; 1,34</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 11,27</t>
+          <t>-1,81; 7,97</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-11,25; -1,66</t>
+          <t>-7,5; -0,09</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 0,37</t>
+          <t>-6,11; 2,19</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,79; 8,43</t>
+          <t>0,31; 8,51</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,73; -1,95</t>
+          <t>-7,65; -2,08</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,66; -0,24</t>
+          <t>-6,46; -0,01</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>63,13%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-68,45%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-43,7%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>61,91%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-63,58%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-39,6%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>63,13%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-68,45%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-49,11%</t>
+          <t>-39,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-44,88%</t>
+          <t>-41,76%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 285,63</t>
+          <t>-3,72; 204,86</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-92,44; 20,96</t>
+          <t>-89,49; -17,65</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-79,17; 86,66</t>
+          <t>-76,75; 28,76</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 199,86</t>
+          <t>-25,85; 235,35</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-89,7; -9,68</t>
+          <t>-91,31; 26,54</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-78,12; 19,84</t>
+          <t>-78,15; 97,64</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,54; 166,36</t>
+          <t>-0,31; 155,09</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-84,35; -33,64</t>
+          <t>-84,68; -34,53</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-70,21; 3,33</t>
+          <t>-69,3; 4,29</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-2,81</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-0,96</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-4,6</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>0,32</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-1,17</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-2,47</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-2,81</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-0,96</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-4,62</t>
+          <t>-2,43</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-3,57</t>
+          <t>-3,54</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 3,27</t>
+          <t>-6,11; 0,26</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 1,23</t>
+          <t>-4,55; 2,54</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,42; -0,16</t>
+          <t>-7,83; -1,89</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 0,12</t>
+          <t>-2,9; 3,4</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 2,71</t>
+          <t>-4,0; 1,24</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,99; -1,99</t>
+          <t>-5,3; 0,16</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 0,93</t>
+          <t>-3,48; 1,04</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 1,18</t>
+          <t>-3,41; 1,01</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-5,55; -1,78</t>
+          <t>-5,73; -1,82</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-54,08%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-18,51%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-88,5%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>10,23%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-37,95%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-80,08%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-54,08%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-18,51%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-88,87%</t>
+          <t>-78,82%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-85,7%</t>
+          <t>-85,01%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-63,56; 197,4</t>
+          <t>-82,64; 16,76</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-85,11; 117,02</t>
+          <t>-64,95; 76,32</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 197,65</t>
+          <t>-100,0; -21,23</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-85,42; 27,28</t>
+          <t>-63,86; 250,34</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-65,75; 83,78</t>
+          <t>-81,64; 98,53</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -34,3</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-65,7; 38,1</t>
+          <t>-65,24; 37,76</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-59,44; 42,52</t>
+          <t>-61,29; 37,47</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -36,98</t>
+          <t>-100,0; -40,94</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>3,33</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,96</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-3,26</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>2,09</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-1,86</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-2,6</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>3,33</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-0,96</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-3,28</t>
+          <t>-2,45</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-2,94</t>
+          <t>-2,86</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,37</t>
+          <t>1,08; 5,69</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -0,04</t>
+          <t>-2,94; 1,02</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-4,37; -0,96</t>
+          <t>-5,24; -1,42</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,68</t>
+          <t>-0,05; 4,07</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,91</t>
+          <t>-3,79; -0,17</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-5,14; -1,33</t>
+          <t>-4,05; -0,66</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,19</t>
+          <t>1,08; 4,21</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-2,61; -0,07</t>
+          <t>-2,94; -0,09</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-4,31; -1,73</t>
+          <t>-4,18; -1,53</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>51,76%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-14,92%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-50,61%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>40,31%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-35,79%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-50,24%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>51,76%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-14,92%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-50,94%</t>
+          <t>-47,26%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-50,45%</t>
+          <t>-49,07%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0,09; 101,47</t>
+          <t>13,16; 100,17</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-57,18; 1,69</t>
+          <t>-39,9; 17,91</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-70,82; -21,23</t>
+          <t>-68,79; -21,19</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>14,44; 101,7</t>
+          <t>-1,32; 95,65</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-40,33; 15,84</t>
+          <t>-60,67; -3,57</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-68,33; -23,97</t>
+          <t>-67,11; -14,14</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>14,46; 78,68</t>
+          <t>15,59; 79,9</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-41,54; -1,14</t>
+          <t>-43,63; -1,56</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-64,94; -32,89</t>
+          <t>-63,21; -30,32</t>
         </is>
       </c>
     </row>
